--- a/corporate_models/Yapi_Kredi_Credit_Model.xlsx
+++ b/corporate_models/Yapi_Kredi_Credit_Model.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit &amp; Recovery Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Bank Financials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +32,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="001B365D"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -40,14 +50,20 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,26 +72,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00244062"/>
-        <bgColor rgb="00244062"/>
+        <fgColor rgb="00F2F4F8"/>
+        <bgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-        <bgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF1DE"/>
-        <bgColor rgb="00EBF1DE"/>
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,32 +99,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,319 +504,759 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Yapı ve Kredi Bankası (Turkey) — Institutional Credit &amp; Recovery Model</t>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Yapı ve Kredi Bankası</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Company &amp; Credit Profile</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Capital Structure ($M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Commercial Banking</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Cash &amp; Equivalents</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>10500</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CEMBI CEEMEA Financial Institutions Assessment | Country: Turkey | Benchmark: YKBNK 6.75% 2029</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Credit Rating</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>BB- / B1</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TRADING BENCHMARK</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>YIELD / SPREAD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Senior Secured Debt</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
+          <t>PRUDENTIAL STANDING</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>STRATEGY STANCE</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Trade Recommendation</t>
-        </is>
-      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>OVERWEIGHT</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Senior Unsecured Bonds</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>3900</v>
+          <t>Benchmark Senior Paper</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>6.75% (+215 bp)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Rating: BB- / B1 | CAR: 17.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Overweight / Core Tier-1 Anchor</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Benchmark Bond Price</t>
-        </is>
-      </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>$98.00</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Bank Syndicated Facilities</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1700</v>
+          <t>Loan Product Mix</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Credit Cards &amp; Consumer (42%), Large Corporate (36%), Commercial &amp; Agri (17%), Leasing (5%)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Asset Quality</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>NPL: 2.1% (Coverage: 102%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Yapı ve Kredi Bankası — 7-Year Prudential &amp; Financial History</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Historical Audited Statements (2021A - 2024A) and Multi-Year Institutional Projections (2025E - 2027E) | USD Millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>BANK FINANCIAL LINE ITEM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2021A</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>I. OPERATING PERFORMANCE &amp; P&amp;L (USD M)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Net Interest Income (NII)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1343.5</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1943</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>2067</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>2232.4</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>2377</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>2480.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Benchmark Bond Yield</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>6.75%</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Total Gross Debt</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>5600</v>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Net Fee &amp; Commission Income</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>520.9</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>593.2</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>665.6</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>723.4</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>781.3</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>832</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>882.6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Price Target / Exit</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>$101.80</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>-4900</v>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Total Operating Income (NII + Fees)</t>
+        </is>
+      </c>
+      <c r="C9" s="11">
+        <f>C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>F7+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>G7+G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="12">
+        <f>H7+H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="12">
+        <f>I7+I8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Hard Invalidation Stop</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>$94.00</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Net Debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>-1.85x</t>
-        </is>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Operating Expenses (Opex)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>742.3</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>869.5</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>975.5</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>1060.4</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1124</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1187.6</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>1251.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Provision Operating Profit (PPOP)</t>
+        </is>
+      </c>
+      <c r="C11" s="11">
+        <f>C9-C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>D9-D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>E9-E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>F9-F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>G9-G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="12">
+        <f>H9-H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="12">
+        <f>I9-I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Net Loan Impairment Provisions</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>351</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>308.9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Earnings &amp; Cash Flow Metric</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>FY Baseline ($M)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Scenario &amp; Recovery Math</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Implied Bond Value ($)</t>
-        </is>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+      <c r="C13" s="13">
+        <f>C11-C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>D11-D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="13">
+        <f>E11-E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="13">
+        <f>F11-F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>G11-G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="14">
+        <f>H11-H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="14">
+        <f>I11-I12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Bull Case (Multiple Expansion / Upgrade)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>$104.80</t>
-        </is>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Net Income / Profit</t>
+        </is>
+      </c>
+      <c r="C14" s="11">
+        <f>C13*0.80</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>D13*0.80</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>E13*0.80</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>F13*0.80</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>G13*0.80</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
+        <f>H13*0.80</f>
+        <v/>
+      </c>
+      <c r="I14" s="12">
+        <f>I13*0.80</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>2650</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Base Case (Pari Passu Debt Servicing)</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>$101.80</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>II. BALANCE SHEET STRUCTURE (USD M)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>48.2%</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Stress Case (Sub-Consensus EBITDA)</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>$88.20</t>
-        </is>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>49104</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>57288</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>63426</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>68200</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>73656</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>78430</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>83204</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Capital Expenditure (Capex)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Distress / Liquidation Floor (Collateral)</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>$73.50</t>
-        </is>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Gross Customer Loans</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>27300</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>31980</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>35880</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>39000</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>42120</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>45240</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>47970</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Net Interest Expense</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>890</v>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Customer Deposits</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>33892</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>38930</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>43052</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>45800</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>49006</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>52212</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>54960</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA / Interest Coverage</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2.98x</t>
-        </is>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Total Shareholders' Equity (Core Tier-1)</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>5565.1</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>6547.2</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>7365.6</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>8184</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>9166.1</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>10148.2</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>11130.2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Free Cash Flow (FCF)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1550</v>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>III. PRUDENTIAL &amp; REGULATORY RATIOS (2021A - 2027E)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Net Interest Margin (NIM %)</t>
+        </is>
+      </c>
+      <c r="C21" s="15">
+        <f>C7/C17</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>D7/D17</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>E7/E17</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>F7/F17</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>G7/G17</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>H7/H17</f>
+        <v/>
+      </c>
+      <c r="I21" s="16">
+        <f>I7/I17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Cost-to-Income Ratio (CIR %)</t>
+        </is>
+      </c>
+      <c r="C22" s="17">
+        <f>C10/C9</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>D10/D9</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>E10/E9</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>F10/F9</f>
+        <v/>
+      </c>
+      <c r="G22" s="18">
+        <f>G10/G9</f>
+        <v/>
+      </c>
+      <c r="H22" s="18">
+        <f>H10/H9</f>
+        <v/>
+      </c>
+      <c r="I22" s="18">
+        <f>I10/I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Return on Equity (ROE %)</t>
+        </is>
+      </c>
+      <c r="C23" s="15">
+        <f>C14/C19</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>D14/D19</f>
+        <v/>
+      </c>
+      <c r="E23" s="15">
+        <f>E14/E19</f>
+        <v/>
+      </c>
+      <c r="F23" s="15">
+        <f>F14/F19</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>G14/G19</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>H14/H19</f>
+        <v/>
+      </c>
+      <c r="I23" s="16">
+        <f>I14/I19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Return on Assets (ROA %)</t>
+        </is>
+      </c>
+      <c r="C24" s="17">
+        <f>C14/C16</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>D14/D16</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>E14/E16</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>F14/F16</f>
+        <v/>
+      </c>
+      <c r="G24" s="18">
+        <f>G14/G16</f>
+        <v/>
+      </c>
+      <c r="H24" s="18">
+        <f>H14/H16</f>
+        <v/>
+      </c>
+      <c r="I24" s="18">
+        <f>I14/I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Loan-to-Deposit Ratio (LDR %)</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>C17/C18</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>D17/D18</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>E17/E18</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>F17/F18</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>G17/G18</f>
+        <v/>
+      </c>
+      <c r="H25" s="18">
+        <f>H17/H18</f>
+        <v/>
+      </c>
+      <c r="I25" s="18">
+        <f>I17/I18</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>